--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataValidation.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataValidation.xlsx
@@ -418,7 +418,7 @@
       <x:c r="C6" s="0" t="s"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="9">
+  <x:dataValidations count="7">
     <x:dataValidation type="whole" errorStyle="warning" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Number out of range" error="This cell only allows the number 2." promptTitle="" prompt="" sqref="A2:A3">
       <x:formula1>2</x:formula1>
       <x:formula2/>
@@ -434,14 +434,6 @@
     <x:dataValidation type="decimal" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A1:A1">
       <x:formula1>1</x:formula1>
       <x:formula2>5</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="none" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="C1:C1">
-      <x:formula1/>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="none" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="C2:C2">
-      <x:formula1/>
-      <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="date" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="Can't party like it's 1999." prompt="Please enter a date in this century." sqref="A4:A4">
       <x:formula1>36526</x:formula1>
@@ -960,18 +952,10 @@
       <x:c r="A6" s="0" t="s"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="6">
+  <x:dataValidations count="4">
     <x:dataValidation type="decimal" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A1:A1">
       <x:formula1>1</x:formula1>
       <x:formula2>5</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="none" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="C1:C1">
-      <x:formula1/>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="none" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="C2:C2">
-      <x:formula1/>
-      <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="date" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="Can't party like it's 1999." prompt="Please enter a date in this century." sqref="A4:A4">
       <x:formula1>36526</x:formula1>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataValidation.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataValidation.xlsx
@@ -772,7 +772,14 @@
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>
@@ -918,7 +925,14 @@
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataValidation.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataValidation.xlsx
@@ -36,7 +36,14 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="1">
+  <x:fonts count="2">
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataValidation.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataValidation.xlsx
@@ -447,7 +447,7 @@
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A5:A5">
-      <x:formula1>$C$1:$C$2</x:formula1>
+      <x:formula1>'Data Validation'!$C$1:$C$2</x:formula1>
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A6:A6">
@@ -760,7 +760,7 @@
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A5:A5">
-      <x:formula1>$C$1:$C$2</x:formula1>
+      <x:formula1>'Data Validation'!$C$1:$C$2</x:formula1>
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A6:A6">
@@ -983,7 +983,7 @@
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A5:A5">
-      <x:formula1>$C$1:$C$2</x:formula1>
+      <x:formula1>'Data Validation'!$C$1:$C$2</x:formula1>
       <x:formula2/>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A6:A6">

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataValidation.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataValidation.xlsx
@@ -86,19 +86,19 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataValidation.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/DataValidation.xlsx
@@ -422,7 +422,6 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s"/>
-      <x:c r="C6" s="0" t="s"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="7">
@@ -533,7 +532,6 @@
       <x:c r="C14" s="1" t="s"/>
       <x:c r="D14" s="1" t="s"/>
       <x:c r="E14" s="1" t="s"/>
-      <x:c r="G14" s="0" t="s"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="42">
